--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,11 +32,6 @@
       <b val="1"/>
       <color rgb="00111827"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="009CA3AF"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -100,21 +95,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -498,226 +492,212 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※ 예시값 — 표기 금액·요율·상호는 전부 예시이며 실제 거래 기록이 아니다. 수수료율은 미확정이고 할인율 0.11%는 예정값이다.</t>
-        </is>
-      </c>
-    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>정산예정일</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>상환액</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>투자실행금</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>투자 수익</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>W금융일수</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Ty수익율</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>179096790</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>178900000</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>196790</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="5" t="n">
         <v>11.4</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="6" t="n">
         <v>0.0352</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>172789860</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>172600000</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>189860</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="5" t="n">
         <v>11.1</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="6" t="n">
         <v>0.0362</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>165481830</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>165300000</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>181830</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="6" t="n">
         <v>0.0368</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>187906470</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>187700000</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>206470</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>11.6</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="6" t="n">
         <v>0.0346</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>183301410</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>183100000</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>201410</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
         <v>11.3</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="6" t="n">
         <v>0.0355</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>176794260</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>176600000</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>194260</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="5" t="n">
         <v>11.2</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="6" t="n">
         <v>0.0358</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <v>186805260</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>186600000</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>205260</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="5" t="n">
         <v>11.5</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="6" t="n">
         <v>0.0349</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="8" t="n">
         <v>1252175880</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>1250800000</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>1375880</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="10" t="n">
         <v>0.0355</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>※ 합계행의 W금융일수·Ty수익율은 투자금액 가중평균(단순평균 아님) — 11.3일 / 3.55%.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -540,10 +540,10 @@
         <v>196790</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0352</v>
+        <v>0.1384</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         <v>189860</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>11.1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="6">
@@ -584,10 +584,10 @@
         <v>181830</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>10.9</v>
+        <v>3.2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="7">
@@ -606,10 +606,10 @@
         <v>206470</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11.6</v>
+        <v>3.3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0346</v>
+        <v>0.1217</v>
       </c>
     </row>
     <row r="8">
@@ -628,10 +628,10 @@
         <v>201410</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>11.3</v>
+        <v>3.1</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0355</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         <v>194260</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>11.2</v>
+        <v>3.2</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="10">
@@ -672,10 +672,10 @@
         <v>205260</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="11">
@@ -694,10 +694,10 @@
         <v>1375880</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>11.3</v>
+        <v>3.1</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.0355</v>
+        <v>0.1295</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>179096790</v>
+        <v>502181933</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>178900000</v>
+        <v>501630140</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>196790</v>
+        <v>551793</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1384</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>172789860</v>
+        <v>502273512</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>172600000</v>
+        <v>501721619</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>189860</v>
+        <v>551893</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="6">
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>165481830</v>
+        <v>500655503</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>165300000</v>
+        <v>500105388</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>181830</v>
+        <v>550115</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.2</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>187906470</v>
+        <v>509267311</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>187700000</v>
+        <v>508707733</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>206470</v>
+        <v>559578</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1217</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>183301410</v>
+        <v>508531838</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>183100000</v>
+        <v>507973068</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>201410</v>
+        <v>558770</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1295</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="9">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>176794260</v>
+        <v>502667677</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>176600000</v>
+        <v>502115351</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>194260</v>
+        <v>552326</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1255</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="10">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>186805260</v>
+        <v>489356048</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>186600000</v>
+        <v>488818348</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>205260</v>
+        <v>537700</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>3</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1252175880</v>
+        <v>3514933822</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1250800000</v>
+        <v>3511071647</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1375880</v>
+        <v>3862175</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3.1</v>

--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>502181933</v>
+        <v>502182540</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>501630140</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>551793</v>
+        <v>552400</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1255</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>502273512</v>
+        <v>502274120</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>501721619</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>551893</v>
+        <v>552501</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1255</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>500655503</v>
+        <v>500656109</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>500105388</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>550115</v>
+        <v>550721</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1255</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>509267311</v>
+        <v>509267927</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>508707733</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>559578</v>
+        <v>560194</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1295</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>508531838</v>
+        <v>508532453</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>507973068</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>558770</v>
+        <v>559385</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="9">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>502667677</v>
+        <v>502668286</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>502115351</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>552326</v>
+        <v>552935</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="10">
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>489356048</v>
+        <v>489356640</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>488818348</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>537700</v>
+        <v>538292</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="11">
@@ -685,19 +685,19 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>3514933822</v>
+        <v>3514938075</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>3511071647</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>3862175</v>
+        <v>3866428</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3.1</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.1295</v>
+        <v>0.1297</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -103,11 +101,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -531,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>502182540</v>
+        <v>28983467</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>501630140</v>
+        <v>28967315</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>552400</v>
+        <v>16152</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1256</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>502274120</v>
+        <v>28394779</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>501721619</v>
+        <v>28379316</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>552501</v>
+        <v>15463</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1256</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>500656109</v>
+        <v>28321159</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>500105388</v>
+        <v>28305968</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>550721</v>
+        <v>15191</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1256</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>509267927</v>
+        <v>28286767</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>508707733</v>
+        <v>28271934</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>560194</v>
+        <v>14833</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1297</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>508532453</v>
+        <v>28551322</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>507973068</v>
+        <v>28536546</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>559385</v>
+        <v>14776</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.134</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="9">
@@ -641,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>502668286</v>
+        <v>28792680</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>502115351</v>
+        <v>28777939</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>552935</v>
+        <v>14741</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.134</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="10">
@@ -663,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>489356640</v>
+        <v>29129472</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>488818348</v>
+        <v>29114508</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>538292</v>
+        <v>14964</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.134</v>
+        <v>0.0668</v>
       </c>
     </row>
     <row r="11">
@@ -685,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>3514938075</v>
+        <v>200459646</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>3511071647</v>
+        <v>200353526</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>3866428</v>
+        <v>106120</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.1297</v>
+        <v>0.06909999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>28983467</v>
+        <v>25951644</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>28967315</v>
+        <v>25941773</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>16152</v>
+        <v>9871</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.76</v>
+        <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0737</v>
+        <v>0.0454</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>28394779</v>
+        <v>25375335</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>28379316</v>
+        <v>25366208</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>15463</v>
+        <v>9127</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>28321159</v>
+        <v>25188287</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>28305968</v>
+        <v>25179655</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>15191</v>
+        <v>8632</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.79</v>
+        <v>3.12</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0702</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>28286767</v>
+        <v>25281442</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>28271934</v>
+        <v>25273193</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>14833</v>
+        <v>8249</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0684</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28551322</v>
+        <v>25602099</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28536546</v>
+        <v>25593903</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14776</v>
+        <v>8196</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2.81</v>
+        <v>3.13</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0673</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="9">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>28792680</v>
+        <v>26102543</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>28777939</v>
+        <v>26094204</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>14741</v>
+        <v>8339</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0663</v>
+        <v>0.0374</v>
       </c>
     </row>
     <row r="10">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>29129472</v>
+        <v>26530744</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>29114508</v>
+        <v>26521983</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14964</v>
+        <v>8761</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0668</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>200459646</v>
+        <v>180032094</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>200353526</v>
+        <v>179970919</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>106120</v>
+        <v>61175</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0399</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>25951644</v>
+        <v>25970340</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>25941773</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9871</v>
+        <v>28567</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0454</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>25375330</v>
+        <v>25394136</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>25366208</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>9127</v>
+        <v>27933</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0424</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>25188289</v>
+        <v>25207385</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>25179655</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8632</v>
+        <v>27728</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>25281449</v>
+        <v>25301031</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>25273193</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8249</v>
+        <v>27831</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.1287</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25602105</v>
+        <v>25622093</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>25593903</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8196</v>
+        <v>28184</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>3.13</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0374</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="9">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>26102548</v>
+        <v>26122944</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>26094204</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8339</v>
+        <v>28735</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0373</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="10">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>26530746</v>
+        <v>26551191</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>26521983</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8761</v>
+        <v>29206</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>3.11</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0388</v>
+        <v>0.1294</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>180032111</v>
+        <v>180169120</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>179970919</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>61175</v>
+        <v>198184</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3.11</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.1293</v>
       </c>
     </row>
   </sheetData>
